--- a/debug/judgements_intro/excel_overviews/gpt-4.1_vs_Qwen2-0.5B-Instruct/Llama-3.3-70B-Instruct/aae/total_votes_file.xlsx
+++ b/debug/judgements_intro/excel_overviews/gpt-4.1_vs_Qwen2-0.5B-Instruct/Llama-3.3-70B-Instruct/aae/total_votes_file.xlsx
@@ -450,10 +450,10 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D3">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E3">
         <v>0</v>
